--- a/data/trans_orig/IP18E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18E-Estudios-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>66694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>68617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137957</t>
+          <t>137865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142293</t>
+          <t>142289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341149</t>
+          <t>341418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>354318</t>
+          <t>354555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376036</t>
+          <t>375891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>390831</t>
+          <t>390378</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>723881</t>
+          <t>722880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>741707</t>
+          <t>741670</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124695</t>
+          <t>125531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138169</t>
+          <t>138844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106832</t>
+          <t>105750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120676</t>
+          <t>120251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236931</t>
+          <t>236821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255133</t>
+          <t>256242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30714</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>50271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>30672</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50432</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>559159</t>
+          <t>559176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>579433</t>
+          <t>579435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1106733</t>
+          <t>1106676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1133410</t>
+          <t>1134445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83738</t>
+          <t>83720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75430</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160663</t>
+          <t>161362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>398255</t>
+          <t>398009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>411937</t>
+          <t>412384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>441018</t>
+          <t>441025</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>455325</t>
+          <t>455621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>845806</t>
+          <t>845040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>865471</t>
+          <t>864500</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130942</t>
+          <t>130354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144127</t>
+          <t>143401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138873</t>
+          <t>138074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152654</t>
+          <t>151693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274521</t>
+          <t>275132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292750</t>
+          <t>292708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18138</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,47 +5223,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>45634</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>35068</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>57318</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>45634</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>35120</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>58402</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>662403</t>
+          <t>662898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>682176</t>
+          <t>682766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1289666</t>
+          <t>1290116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1317211</t>
+          <t>1317305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58440</t>
+          <t>58075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111449</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117180</t>
+          <t>117168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>411177</t>
+          <t>411911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>424517</t>
+          <t>425098</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,82 +6670,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>421787</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>414810</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>427111</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>841045</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>830428</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>848586</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>97,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>421787</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>414206</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>427011</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>841045</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>830936</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>848922</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127863</t>
+          <t>126999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141384</t>
+          <t>140825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138134</t>
+          <t>137748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153258</t>
+          <t>153369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271414</t>
+          <t>270989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>291000</t>
+          <t>290745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71207</t>
+          <t>71711</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85082</t>
+          <t>84943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90261</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133398</t>
+          <t>135719</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150024</t>
+          <t>150255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51778</t>
+          <t>51561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">

--- a/data/trans_orig/IP18E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18E-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la organización para la que trabaja el médico que le atendió en 2007 (tasa de respuesta: 98,15%)</t>
+          <t>Menores según el régimen de financiación de la última consulta médica a la que acudió en 2007 (tasa de respuesta: 98,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4017</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1062,74 +1062,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71345</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68616</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72031</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>69611</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>66694</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67218</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>70711</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>71345</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68617</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72031</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>210</t>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137865</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142289</t>
+          <t>142288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1175,57 +1175,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72031</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72031</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72031</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>70711</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>70711</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>70711</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>72031</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72031</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>72031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1410,67 +1410,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>10790</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5840</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16594</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>9656</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5511</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16163</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5486</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15039</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10790</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6294</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17652</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28569</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1518,72 +1518,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8153</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7110</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12133</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11895</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8153</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4667</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14581</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1631,72 +1631,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>384448</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>376930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>390597</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>348883</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>341418</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>354555</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>342451</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>354648</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>95,41%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>384448</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>375891</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>390378</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>722880</t>
+          <t>722663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>741670</t>
+          <t>741942</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1744,57 +1744,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>403391</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>403391</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>403391</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>551</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>365650</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>365650</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>365650</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>403391</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>403391</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>403391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1866,102 +1866,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3898</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4760</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4306</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1979,67 +1979,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>8770</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4560</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14071</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>8793</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4702</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>14064</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14135</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>8770</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>14824</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2087,72 +2087,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13607</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8706</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20506</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>10551</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5903</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15967</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16497</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13607</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>8541</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20063</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -2200,72 +2200,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114116</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>106190</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,19%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>132593</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>138844</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>125371</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>138914</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,88%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>114116</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>105750</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>120251</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236821</t>
+          <t>236460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256242</t>
+          <t>255948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -2313,57 +2313,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>137178</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>137178</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>137178</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>152620</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>152620</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>152620</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>137178</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>137178</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>137178</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2435,102 +2435,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3417</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3767</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4793</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2543,72 +2543,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20246</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13212</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27747</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>19550</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13417</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>27786</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>13863</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>28232</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>20246</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>14181</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>29030</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>30838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50271</t>
+          <t>50830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2656,72 +2656,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>21760</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>15945</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>29900</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>17661</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>12233</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>25978</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>11993</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>25482</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>3,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>21760</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>14997</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>30672</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>50472</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2769,72 +2769,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>569909</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>559204</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>579120</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>91,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>820</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>551087</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>541509</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>559492</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>540683</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>559911</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>93,57%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>859</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>569909</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>559176</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>579435</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1106676</t>
+          <t>1106135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1134445</t>
+          <t>1134499</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2882,57 +2882,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>612599</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>612599</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>612599</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>878</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>588981</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>588981</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>588981</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>612599</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>612599</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>612599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3045,13 +3045,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la organización para la que trabaja el médico que le atendió en 2012 (tasa de respuesta: 98,65%)</t>
+          <t>Menores según el régimen de financiación de la última consulta médica a la que acudió en 2012 (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3062,7 +3062,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3343,107 +3343,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3393</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3669</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3456,107 +3456,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3079</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3912</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3382</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3569,74 +3569,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77639</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74496</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78293</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>86435</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>83720</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>83675</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>87113</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77639</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>75214</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78293</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>234</t>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161362</t>
+          <t>160814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3682,57 +3682,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78293</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78293</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87113</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>87113</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>87113</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>78293</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>78293</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3799,72 +3799,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4597</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3912,64 +3912,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7880</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13081</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7767</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13244</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4048</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14524</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7880</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4472</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13814</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4025,72 +4025,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10550</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6013</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17093</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8875</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5038</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15276</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4790</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15142</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10550</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5790</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>17085</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4138,72 +4138,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>449400</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>441660</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>455223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>406266</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>398009</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>412384</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>397654</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>411836</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>95,86%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>449400</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>441025</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>455621</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>845040</t>
+          <t>845182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>864500</t>
+          <t>864794</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -4251,57 +4251,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>467830</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>467830</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>467830</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>614</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>423834</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>423834</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>423834</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>467830</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>467830</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>467830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4368,107 +4368,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2662</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4486,67 +4486,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>4771</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>4887</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9982</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9447</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>4771</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>9455</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -4594,72 +4594,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14145</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21871</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11409</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7156</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18069</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17477</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14145</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9116</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21223</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -4707,72 +4707,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138292</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>152240</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>138114</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130354</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143401</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>131113</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>144150</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146120</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>138074</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>151693</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275132</t>
+          <t>273942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292708</t>
+          <t>293049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -4820,57 +4820,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>155066</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>155066</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>155066</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4937,107 +4937,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1581</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5995</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5518</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1581</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1581</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5055,69 +5055,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>12651</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7665</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19074</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>13332</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7860</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20212</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8249</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>20148</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>12651</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>7883</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>19496</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>38</t>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5163,107 +5163,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>25349</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>18408</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>34334</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>20285</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14014</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>29350</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>13467</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>28420</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>3,05%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>25349</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>18402</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>33814</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>45634</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>35618</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>58029</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>45634</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>35068</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>57318</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5276,72 +5276,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>673159</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>661988</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>681183</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>94,66%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>93,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,78%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>909</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>630816</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>619523</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>640023</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>620886</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>639611</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>94,72%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>673159</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>662898</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>682766</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1290116</t>
+          <t>1289319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1317305</t>
+          <t>1317437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -5389,57 +5389,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>711159</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>711159</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>711159</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>959</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>666014</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>666014</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>666014</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>711159</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>711159</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>711159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5552,13 +5552,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la organización para la que trabaja el médico que le atendió en 2016 (tasa de respuesta: 98,57%)</t>
+          <t>Menores según el régimen de financiación de la última consulta médica a la que acudió en 2016 (tasa de respuesta: 98,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5569,7 +5569,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5850,107 +5850,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3552</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2627</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5963,72 +5963,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1332</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4385</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>537</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -6076,74 +6076,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61290</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>62497</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>53980</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>50569</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>50927</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>55312</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>97,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61290</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>58075</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>62497</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>111385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117168</t>
+          <t>117087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6189,57 +6189,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>62497</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62497</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62497</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>55312</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>55312</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>55312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>62497</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>62497</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>62497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6419,72 +6419,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5411</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9937</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10232</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7150</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6532,72 +6532,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11480</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>12207</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7606</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19334</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7530</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18562</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11480</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6794</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18171</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>32072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6645,72 +6645,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>421787</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>414413</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>426762</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>419257</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>411911</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>425098</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>411346</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>424785</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>95,97%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>421787</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>414810</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>427111</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>830428</t>
+          <t>832020</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>848586</t>
+          <t>848503</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -6758,57 +6758,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>436410</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>436410</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>436410</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>436875</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>436875</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>436875</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>436410</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>436410</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>436410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6988,72 +6988,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10022</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>4659</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9046</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9583</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>5538</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11108</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7101,72 +7101,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18033</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12480</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25142</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>14870</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9648</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21671</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9569</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21995</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18033</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12016</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25427</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42988</t>
+          <t>44095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -7214,72 +7214,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146581</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138818</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>152909</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>135098</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>126999</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>140825</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>127303</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>141093</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146581</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>137748</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>153369</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270989</t>
+          <t>270403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>290745</t>
+          <t>290686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -7327,57 +7327,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>170152</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>170152</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>170152</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>154627</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>154627</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>154627</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>170152</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>170152</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>170152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7557,72 +7557,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9326</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5389</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15164</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10070</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5902</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16344</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15851</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9326</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>5304</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14876</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7670,72 +7670,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30075</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>22956</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>40212</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>28409</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20795</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38130</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>20928</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>37763</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>4,39%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>30075</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>22614</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>38859</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>46502</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71711</t>
+          <t>71712</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -7783,74 +7783,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>629659</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>618449</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>637528</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,29%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>608336</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>597539</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>616918</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>597997</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>616903</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>94,05%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>95,38%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>629659</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>619529</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>638715</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1811</t>
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1222887</t>
+          <t>1223094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1251511</t>
+          <t>1251904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -7896,57 +7896,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>669060</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>669060</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>669060</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>974</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>646814</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>646814</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>646814</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>669060</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>669060</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>669060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8059,13 +8059,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la organización para la que trabaja el médico que le atendió en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según el régimen de financiación de la última consulta médica a la que acudió en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8076,7 +8076,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8244,107 +8244,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -8583,74 +8583,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6154</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4065</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>94,29%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9434</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -8658,27 +8658,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8696,57 +8696,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8926,72 +8926,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7809</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17252</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -9039,72 +9039,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6194</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -9152,72 +9152,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>81168</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77145</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82761</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>56317</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46938</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>61201</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>85,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>70,86%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88447</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84943</t>
+          <t>50673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90275</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>144764</t>
+          <t>137077</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135719</t>
+          <t>131288</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150255</t>
+          <t>141228</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -9265,57 +9265,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9495,72 +9495,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2943</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -9608,72 +9608,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2346</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -9721,72 +9721,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23652</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18922</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26613</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>21679</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17746</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>78,74%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>20809</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28556</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47265</t>
+          <t>44460</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40805</t>
+          <t>38702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51561</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -9834,57 +9834,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9951,107 +9951,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10064,72 +10064,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8360</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>11315</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>21697</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -10290,72 +10290,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>113911</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>108246</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>117463</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>84150</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>73912</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>89845</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>73,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>123465</t>
+          <t>82331</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117893</t>
+          <t>76433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127020</t>
+          <t>87252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>207615</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196061</t>
+          <t>187788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215028</t>
+          <t>202132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -10403,57 +10403,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
